--- a/letture_settimanali/Riepilogo_Annuale_2026.xlsx
+++ b/letture_settimanali/Riepilogo_Annuale_2026.xlsx
@@ -1300,16 +1300,14 @@
       </c>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>3</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G4" s="9" t="n"/>
       <c r="H4" s="9" t="n"/>
@@ -1325,7 +1323,7 @@
         <v>45</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="S4" s="10" t="n"/>
       <c r="T4" s="10" t="n"/>
@@ -1334,7 +1332,7 @@
       <c r="W4" s="10" t="n"/>
       <c r="X4" s="10" t="n"/>
       <c r="Y4" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z4" s="9" t="n"/>
       <c r="AA4" s="9" t="n"/>
@@ -1351,12 +1349,12 @@
       <c r="AL4" s="9" t="n"/>
       <c r="AM4" s="9" t="n"/>
       <c r="AN4" s="9" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AO4" s="9" t="n"/>
       <c r="AP4" s="9" t="n"/>
       <c r="AQ4" s="9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AR4" s="9" t="n">
         <v>1</v>
@@ -1395,16 +1393,14 @@
       </c>
       <c r="BL4" s="12" t="n"/>
       <c r="BM4" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN4" s="12" t="n">
-        <v>1.2</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="BN4" s="12" t="n"/>
       <c r="BO4" s="12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" s="13" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="BQ4" s="12" t="n"/>
       <c r="BR4" s="12" t="n"/>
@@ -1420,7 +1416,7 @@
         <v>18</v>
       </c>
       <c r="CB4" s="13" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="CC4" s="13" t="n"/>
       <c r="CD4" s="13" t="n"/>
@@ -1429,7 +1425,7 @@
       <c r="CG4" s="13" t="n"/>
       <c r="CH4" s="13" t="n"/>
       <c r="CI4" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CJ4" s="12" t="n"/>
       <c r="CK4" s="12" t="n"/>
@@ -1446,12 +1442,12 @@
       <c r="CV4" s="12" t="n"/>
       <c r="CW4" s="12" t="n"/>
       <c r="CX4" s="12" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="CY4" s="12" t="n"/>
       <c r="CZ4" s="12" t="n"/>
       <c r="DA4" s="12" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="DB4" s="12" t="n">
         <v>0.4</v>
@@ -1510,10 +1506,10 @@
       <c r="O5" s="10" t="n"/>
       <c r="P5" s="10" t="n"/>
       <c r="Q5" s="9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="S5" s="10" t="n"/>
       <c r="T5" s="10" t="n"/>
@@ -1522,7 +1518,7 @@
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="10" t="n"/>
       <c r="Y5" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z5" s="9" t="n"/>
       <c r="AA5" s="9" t="n"/>
@@ -1551,7 +1547,7 @@
         <v>3</v>
       </c>
       <c r="AT5" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AU5" s="9" t="n"/>
       <c r="AV5" s="10" t="n"/>
@@ -1603,10 +1599,10 @@
       <c r="BY5" s="13" t="n"/>
       <c r="BZ5" s="13" t="n"/>
       <c r="CA5" s="12" t="n">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="CB5" s="13" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="CC5" s="13" t="n"/>
       <c r="CD5" s="13" t="n"/>
@@ -1615,7 +1611,7 @@
       <c r="CG5" s="13" t="n"/>
       <c r="CH5" s="13" t="n"/>
       <c r="CI5" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CJ5" s="12" t="n"/>
       <c r="CK5" s="12" t="n"/>
@@ -1644,7 +1640,7 @@
         <v>1.2</v>
       </c>
       <c r="DD5" s="12" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="DE5" s="12" t="n"/>
       <c r="DF5" s="13" t="n"/>
@@ -1680,11 +1676,11 @@
       </c>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="9" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -1698,7 +1694,7 @@
       <c r="O6" s="10" t="n"/>
       <c r="P6" s="10" t="n"/>
       <c r="Q6" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>46</v>
@@ -1737,7 +1733,7 @@
       <c r="AR6" s="9" t="n"/>
       <c r="AS6" s="9" t="n"/>
       <c r="AT6" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU6" s="9" t="n"/>
       <c r="AV6" s="10" t="n"/>
@@ -1769,11 +1765,11 @@
       </c>
       <c r="BL6" s="12" t="n"/>
       <c r="BM6" s="12" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="BN6" s="12" t="n"/>
       <c r="BO6" s="12" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="BP6" s="13" t="n"/>
       <c r="BQ6" s="12" t="n"/>
@@ -1787,7 +1783,7 @@
       <c r="BY6" s="13" t="n"/>
       <c r="BZ6" s="13" t="n"/>
       <c r="CA6" s="12" t="n">
-        <v>42.4</v>
+        <v>44.8</v>
       </c>
       <c r="CB6" s="13" t="n">
         <v>18.4</v>
@@ -1826,7 +1822,7 @@
       <c r="DB6" s="12" t="n"/>
       <c r="DC6" s="12" t="n"/>
       <c r="DD6" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DE6" s="12" t="n"/>
       <c r="DF6" s="13" t="n"/>
@@ -1878,7 +1874,7 @@
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
       <c r="Q7" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>44</v>
@@ -1890,7 +1886,7 @@
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="10" t="n"/>
       <c r="Y7" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="9" t="n"/>
       <c r="AA7" s="9" t="n"/>
@@ -1914,12 +1910,12 @@
       <c r="AO7" s="9" t="n"/>
       <c r="AP7" s="9" t="n"/>
       <c r="AQ7" s="9" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AR7" s="9" t="n"/>
       <c r="AS7" s="9" t="n"/>
       <c r="AT7" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU7" s="9" t="n"/>
       <c r="AV7" s="10" t="n"/>
@@ -1971,7 +1967,7 @@
       <c r="BY7" s="13" t="n"/>
       <c r="BZ7" s="13" t="n"/>
       <c r="CA7" s="12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB7" s="13" t="n">
         <v>17.6</v>
@@ -1983,7 +1979,7 @@
       <c r="CG7" s="13" t="n"/>
       <c r="CH7" s="13" t="n"/>
       <c r="CI7" s="13" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="CJ7" s="12" t="n"/>
       <c r="CK7" s="12" t="n"/>
@@ -2007,12 +2003,12 @@
       <c r="CY7" s="12" t="n"/>
       <c r="CZ7" s="12" t="n"/>
       <c r="DA7" s="12" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="DB7" s="12" t="n"/>
       <c r="DC7" s="12" t="n"/>
       <c r="DD7" s="12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="DE7" s="12" t="n"/>
       <c r="DF7" s="13" t="n"/>
@@ -2052,7 +2048,7 @@
       </c>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="9" t="n"/>
@@ -2066,10 +2062,10 @@
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
@@ -2089,7 +2085,7 @@
       <c r="AF8" s="9" t="n"/>
       <c r="AG8" s="9" t="n"/>
       <c r="AH8" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="9" t="n"/>
       <c r="AJ8" s="10" t="n"/>
@@ -2097,12 +2093,12 @@
       <c r="AL8" s="9" t="n"/>
       <c r="AM8" s="9" t="n"/>
       <c r="AN8" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO8" s="9" t="n"/>
       <c r="AP8" s="9" t="n"/>
       <c r="AQ8" s="9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AR8" s="9" t="n"/>
       <c r="AS8" s="9" t="n"/>
@@ -2117,7 +2113,7 @@
         </is>
       </c>
       <c r="AX8" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY8" s="9" t="n"/>
       <c r="AZ8" s="9" t="n"/>
@@ -2149,7 +2145,7 @@
       </c>
       <c r="BN8" s="12" t="n"/>
       <c r="BO8" s="12" t="n">
-        <v>18.8</v>
+        <v>20.4</v>
       </c>
       <c r="BP8" s="13" t="n"/>
       <c r="BQ8" s="12" t="n"/>
@@ -2163,10 +2159,10 @@
       <c r="BY8" s="13" t="n"/>
       <c r="BZ8" s="13" t="n"/>
       <c r="CA8" s="12" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="CB8" s="13" t="n">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="CC8" s="13" t="n"/>
       <c r="CD8" s="13" t="n"/>
@@ -2186,7 +2182,7 @@
       <c r="CP8" s="12" t="n"/>
       <c r="CQ8" s="12" t="n"/>
       <c r="CR8" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CS8" s="12" t="n"/>
       <c r="CT8" s="13" t="n"/>
@@ -2194,12 +2190,12 @@
       <c r="CV8" s="12" t="n"/>
       <c r="CW8" s="12" t="n"/>
       <c r="CX8" s="12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="CY8" s="12" t="n"/>
       <c r="CZ8" s="12" t="n"/>
       <c r="DA8" s="12" t="n">
-        <v>9.6</v>
+        <v>11.2</v>
       </c>
       <c r="DB8" s="12" t="n"/>
       <c r="DC8" s="12" t="n"/>
@@ -2214,7 +2210,7 @@
         </is>
       </c>
       <c r="DH8" s="14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="DI8" s="12" t="n"/>
       <c r="DJ8" s="12" t="n"/>
@@ -2244,11 +2240,11 @@
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -2265,7 +2261,7 @@
         <v>35</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
@@ -2298,7 +2294,7 @@
       <c r="AO9" s="9" t="n"/>
       <c r="AP9" s="9" t="n"/>
       <c r="AQ9" s="9" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="AR9" s="9" t="n"/>
       <c r="AS9" s="9" t="n"/>
@@ -2313,7 +2309,7 @@
         </is>
       </c>
       <c r="AX9" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY9" s="9" t="n"/>
       <c r="AZ9" s="9" t="n"/>
@@ -2345,11 +2341,11 @@
       </c>
       <c r="BL9" s="12" t="n"/>
       <c r="BM9" s="12" t="n">
-        <v>19.6</v>
+        <v>22.8</v>
       </c>
       <c r="BN9" s="12" t="n"/>
       <c r="BO9" s="12" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="BP9" s="13" t="n"/>
       <c r="BQ9" s="12" t="n"/>
@@ -2366,7 +2362,7 @@
         <v>14</v>
       </c>
       <c r="CB9" s="13" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="CC9" s="13" t="n"/>
       <c r="CD9" s="13" t="n"/>
@@ -2399,7 +2395,7 @@
       <c r="CY9" s="12" t="n"/>
       <c r="CZ9" s="12" t="n"/>
       <c r="DA9" s="12" t="n">
-        <v>32.4</v>
+        <v>42.8</v>
       </c>
       <c r="DB9" s="12" t="n"/>
       <c r="DC9" s="12" t="n"/>
@@ -2414,7 +2410,7 @@
         </is>
       </c>
       <c r="DH9" s="14" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="DI9" s="12" t="n"/>
       <c r="DJ9" s="12" t="n"/>
@@ -2448,7 +2444,7 @@
       </c>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n">
@@ -2480,7 +2476,7 @@
       <c r="W10" s="10" t="n"/>
       <c r="X10" s="10" t="n"/>
       <c r="Y10" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="9" t="n"/>
       <c r="AA10" s="9" t="n"/>
@@ -2541,7 +2537,7 @@
       </c>
       <c r="BL10" s="12" t="n"/>
       <c r="BM10" s="12" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="BN10" s="12" t="n"/>
       <c r="BO10" s="12" t="n">
@@ -2573,7 +2569,7 @@
       <c r="CG10" s="13" t="n"/>
       <c r="CH10" s="13" t="n"/>
       <c r="CI10" s="13" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="CJ10" s="12" t="n"/>
       <c r="CK10" s="12" t="n"/>
@@ -2763,13 +2759,13 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>14</v>
+        <v>16.4</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>23.6</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>10</v>
@@ -2778,10 +2774,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>19.6</v>
+        <v>22.8</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="7">
@@ -2790,9 +2786,7 @@
           <t>BETULACEAE</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="B7" s="12" t="n"/>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
@@ -2807,22 +2801,22 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>18.8</v>
+        <v>20.4</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>12.8</v>
@@ -2835,7 +2829,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="C9" s="18" t="n"/>
       <c r="D9" s="18" t="n"/>
@@ -2996,16 +2990,16 @@
         <v>18</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>42.4</v>
+        <v>44.8</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>14</v>
@@ -3021,10 +3015,10 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>18.4</v>
@@ -3033,10 +3027,10 @@
         <v>17.6</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="H21" s="13" t="n">
         <v>111.6</v>
@@ -3133,16 +3127,16 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>2.4</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="F28" s="13" t="n">
         <v>4.8</v>
@@ -3151,7 +3145,7 @@
         <v>5.6</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -3279,7 +3273,7 @@
         <v>2.8</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>7.6</v>
@@ -3365,7 +3359,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="C43" s="12" t="n">
         <v>8.800000000000001</v>
@@ -3377,7 +3371,7 @@
         <v>2.8</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>9.199999999999999</v>
@@ -3421,7 +3415,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>32.4</v>
@@ -3430,13 +3424,13 @@
         <v>10</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>9.6</v>
+        <v>11.2</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>32.4</v>
+        <v>42.8</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>12.4</v>
@@ -3486,13 +3480,13 @@
         <v>27.6</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>5.2</v>
@@ -3593,10 +3587,10 @@
         <v>1.6</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H53" s="14" t="n">
         <v>1.6</v>
@@ -3932,13 +3926,13 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>59</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>25</v>
@@ -3947,13 +3941,13 @@
         <v>10</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -3962,18 +3956,14 @@
           <t>BETULACEAE</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
-        <v>3</v>
-      </c>
+      <c r="B7" s="23" t="n"/>
       <c r="C7" s="23" t="n"/>
       <c r="D7" s="23" t="n"/>
       <c r="E7" s="23" t="n"/>
       <c r="F7" s="23" t="n"/>
       <c r="G7" s="23" t="n"/>
       <c r="H7" s="23" t="n"/>
-      <c r="I7" s="23" t="n">
-        <v>3</v>
-      </c>
+      <c r="I7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -3982,28 +3972,28 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>15</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="23" t="n">
         <v>32</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -4013,7 +4003,7 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" s="25" t="n"/>
       <c r="D9" s="25" t="n"/>
@@ -4024,7 +4014,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -4187,16 +4177,16 @@
         <v>45</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>35</v>
@@ -4205,7 +4195,7 @@
         <v>29</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21">
@@ -4215,10 +4205,10 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C21" s="24" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>46</v>
@@ -4227,16 +4217,16 @@
         <v>44</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H21" s="24" t="n">
         <v>279</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>686</v>
+        <v>701</v>
       </c>
     </row>
     <row r="22">
@@ -4336,16 +4326,16 @@
         </is>
       </c>
       <c r="B28" s="24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" s="24" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="24" t="n">
         <v>12</v>
@@ -4354,10 +4344,10 @@
         <v>14</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
@@ -4493,7 +4483,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" s="24" t="n">
         <v>19</v>
@@ -4502,7 +4492,7 @@
         <v>22</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
@@ -4587,7 +4577,7 @@
         </is>
       </c>
       <c r="B43" s="23" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C43" s="23" t="n">
         <v>22</v>
@@ -4599,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>23</v>
@@ -4608,7 +4598,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44">
@@ -4648,7 +4638,7 @@
         </is>
       </c>
       <c r="B46" s="23" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C46" s="23" t="n">
         <v>81</v>
@@ -4657,19 +4647,19 @@
         <v>25</v>
       </c>
       <c r="E46" s="23" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F46" s="23" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="H46" s="23" t="n">
         <v>31</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>459</v>
+        <v>494</v>
       </c>
     </row>
     <row r="47">
@@ -4722,13 +4712,13 @@
         <v>69</v>
       </c>
       <c r="C49" s="23" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E49" s="23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F49" s="23" t="n">
         <v>13</v>
@@ -4740,7 +4730,7 @@
         <v>5</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50">
@@ -4803,16 +4793,16 @@
         <v>4</v>
       </c>
       <c r="F53" s="26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G53" s="26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H53" s="26" t="n">
         <v>4</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
@@ -5138,13 +5128,13 @@
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>14</v>
+        <v>16.4</v>
       </c>
       <c r="C70" s="12" t="n">
         <v>23.6</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>10</v>
@@ -5153,13 +5143,13 @@
         <v>4</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>19.6</v>
+        <v>22.8</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="71">
@@ -5168,18 +5158,14 @@
           <t>BETULACEAE</t>
         </is>
       </c>
-      <c r="B71" s="12" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="B71" s="12" t="n"/>
       <c r="C71" s="12" t="n"/>
       <c r="D71" s="12" t="n"/>
       <c r="E71" s="12" t="n"/>
       <c r="F71" s="12" t="n"/>
       <c r="G71" s="12" t="n"/>
       <c r="H71" s="12" t="n"/>
-      <c r="I71" s="12" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="I71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -5188,28 +5174,28 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="C72" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>6</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>18.8</v>
+        <v>20.4</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>12.8</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="73">
@@ -5219,7 +5205,7 @@
         </is>
       </c>
       <c r="B73" s="13" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="18" t="n"/>
@@ -5230,7 +5216,7 @@
         <v>5.2</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="74">
@@ -5393,16 +5379,16 @@
         <v>18</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>42.4</v>
+        <v>44.8</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>14</v>
@@ -5411,7 +5397,7 @@
         <v>11.6</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="85">
@@ -5421,10 +5407,10 @@
         </is>
       </c>
       <c r="B85" s="13" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="C85" s="13" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="D85" s="13" t="n">
         <v>18.4</v>
@@ -5433,16 +5419,16 @@
         <v>17.6</v>
       </c>
       <c r="F85" s="13" t="n">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="H85" s="13" t="n">
         <v>111.6</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>39.2</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="86">
@@ -5542,16 +5528,16 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="D92" s="13" t="n">
         <v>2.4</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>4.8</v>
@@ -5560,10 +5546,10 @@
         <v>5.6</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="93">
@@ -5699,7 +5685,7 @@
         <v>2.8</v>
       </c>
       <c r="F101" s="13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G101" s="13" t="n">
         <v>7.6</v>
@@ -5708,7 +5694,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="102">
@@ -5793,7 +5779,7 @@
         </is>
       </c>
       <c r="B107" s="12" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="C107" s="12" t="n">
         <v>8.800000000000001</v>
@@ -5805,7 +5791,7 @@
         <v>2.8</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>9.199999999999999</v>
@@ -5814,7 +5800,7 @@
         <v>4.8</v>
       </c>
       <c r="I107" s="12" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="108">
@@ -5854,7 +5840,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="C110" s="12" t="n">
         <v>32.4</v>
@@ -5863,19 +5849,19 @@
         <v>10</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>9.6</v>
+        <v>11.2</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>32.4</v>
+        <v>42.8</v>
       </c>
       <c r="H110" s="12" t="n">
         <v>12.4</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>26.2</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="111">
@@ -5928,13 +5914,13 @@
         <v>27.6</v>
       </c>
       <c r="C113" s="12" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="F113" s="12" t="n">
         <v>5.2</v>
@@ -5946,7 +5932,7 @@
         <v>2</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="114">
@@ -6009,16 +5995,16 @@
         <v>1.6</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H117" s="14" t="n">
         <v>1.6</v>
       </c>
       <c r="I117" s="12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
